--- a/data/Viajes/Pasajeros 06-Jun-2026.xlsx
+++ b/data/Viajes/Pasajeros 06-Jun-2026.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoefe.sharepoint.com/sites/GOFEFEVALPARASO/Documentos compartidos/UNIDAD DE GESTION/Datos Operacionales/Carga Tren/Pasajeros/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoefe.sharepoint.com/sites/GOFEFEVALPARASO/Documentos compartidos/UNIDAD DE GESTION/Datos Operacionales/Carga Tren/Pasajeros/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1" documentId="8_{5E32FDB2-86A1-4732-AA4E-F111A60D6D60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1F15B62-77E1-41F3-9A6B-43215154A6B0}"/>
@@ -2901,12 +2901,16 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
+    <C_x00f3_digo xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3157,22 +3161,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
-    <C_x00f3_digo xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB24654B-EEF5-4E2F-902E-CD6AB81AF804}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C5BA818-F0FF-496D-B882-BA977B7C1DF2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ffac592c-cdc9-47d3-9b5f-572462ebd9e4"/>
+    <ds:schemaRef ds:uri="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3197,12 +3200,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C5BA818-F0FF-496D-B882-BA977B7C1DF2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB24654B-EEF5-4E2F-902E-CD6AB81AF804}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ffac592c-cdc9-47d3-9b5f-572462ebd9e4"/>
-    <ds:schemaRef ds:uri="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>